--- a/corr_matrix/residual_exam1A_3PL.xlsx
+++ b/corr_matrix/residual_exam1A_3PL.xlsx
@@ -429,6 +429,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>1A01</t>
@@ -520,49 +525,49 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.1928854278788132</v>
+        <v>-0.1930351881894874</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.03611300042467083</v>
+        <v>-0.03601397403676533</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.08318533573999363</v>
+        <v>-0.08280435749010209</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1026036603291834</v>
+        <v>-0.1024863268954169</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.1355313016302211</v>
+        <v>-0.1355317025116319</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.1218085247248904</v>
+        <v>-0.1216160843892629</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08073821517666842</v>
+        <v>-0.08052004971915319</v>
       </c>
       <c r="J2" t="n">
-        <v>0.05804995049247332</v>
+        <v>0.05792992845644979</v>
       </c>
       <c r="K2" t="n">
-        <v>0.048575392882437</v>
+        <v>0.04863709424635373</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.09626554706117064</v>
+        <v>-0.09646120289282363</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1487156556928946</v>
+        <v>-0.1484183594555742</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.151685918228377</v>
+        <v>-0.1526585001533138</v>
       </c>
       <c r="O2" t="n">
-        <v>0.100229179268183</v>
+        <v>0.1002349950463313</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1113857471036297</v>
+        <v>-0.1117956020591704</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.05272643549990629</v>
+        <v>0.05294858795777122</v>
       </c>
     </row>
     <row r="3">
@@ -572,52 +577,52 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.1928854278788132</v>
+        <v>-0.1930351881894874</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04218716296693827</v>
+        <v>-0.04224970124804656</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1040418464421135</v>
+        <v>-0.1039047043456229</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.04386877442450642</v>
+        <v>-0.04322215274933858</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02817883678221163</v>
+        <v>0.02807453971139579</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1450430271331672</v>
+        <v>0.1447840044277443</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1340585348376442</v>
+        <v>-0.1341678821627228</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.05074299149698708</v>
+        <v>-0.05046929824311092</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0325394223372264</v>
+        <v>-0.03270193011859826</v>
       </c>
       <c r="L3" t="n">
-        <v>0.08546242073465947</v>
+        <v>0.0850583532950671</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0002664334074884053</v>
+        <v>-0.0001613377742980673</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0003474839180459978</v>
+        <v>0.0004577684142593403</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1868374340694986</v>
+        <v>-0.1867170118357693</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1993983041643551</v>
+        <v>-0.1994977896287584</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2514850807914431</v>
+        <v>-0.2514247683491527</v>
       </c>
     </row>
     <row r="4">
@@ -627,52 +632,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.03611300042467083</v>
+        <v>-0.03601397403676533</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.04218716296693827</v>
+        <v>-0.04224970124804656</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01329776326780032</v>
+        <v>0.01328768241382592</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1064129613104046</v>
+        <v>-0.1063429542279438</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.08553587651272015</v>
+        <v>-0.08512695739713484</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2703772862496451</v>
+        <v>-0.27028864358845</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0805183112230478</v>
+        <v>-0.08049336060092532</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1115211311519058</v>
+        <v>0.1122835094873397</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.07518360906744938</v>
+        <v>-0.07515773676517375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06023104328812207</v>
+        <v>0.0601751418402045</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1478146495693051</v>
+        <v>-0.1478381907239498</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1774285833250369</v>
+        <v>-0.1768872410707682</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01493214900673709</v>
+        <v>0.01536554336623541</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.01156395777272529</v>
+        <v>-0.01183214182746893</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1414652077917651</v>
+        <v>-0.1414849592482887</v>
       </c>
     </row>
     <row r="5">
@@ -682,52 +687,52 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.08318533573999363</v>
+        <v>-0.08280435749010209</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.1040418464421135</v>
+        <v>-0.1039047043456229</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01329776326780032</v>
+        <v>0.01328768241382592</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2342261862061746</v>
+        <v>-0.2337344568345542</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1766286529237518</v>
+        <v>-0.1770074714359857</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.06511969502461017</v>
+        <v>-0.06496619955148661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2706328631736525</v>
+        <v>0.2707204419789068</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.03348565619808058</v>
+        <v>-0.03364491300047812</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1000576880413598</v>
+        <v>0.100031692817402</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2007454882679256</v>
+        <v>-0.2006260126681326</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.03316880020480939</v>
+        <v>-0.03274517515127993</v>
       </c>
       <c r="N5" t="n">
-        <v>0.006469681501478089</v>
+        <v>0.005467479294178872</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1812667506864618</v>
+        <v>-0.1812409067511802</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1351991514369207</v>
+        <v>-0.135727445255063</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.06401031662561422</v>
+        <v>-0.06361767074921351</v>
       </c>
     </row>
     <row r="6">
@@ -737,52 +742,52 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.1026036603291834</v>
+        <v>-0.1024863268954169</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.04386877442450642</v>
+        <v>-0.04322215274933858</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1064129613104046</v>
+        <v>-0.1063429542279438</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2342261862061746</v>
+        <v>-0.2337344568345542</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0922012884699336</v>
+        <v>-0.09632840393371352</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0508629321073147</v>
+        <v>-0.05084429995402844</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1360656205524013</v>
+        <v>-0.1359932351809089</v>
       </c>
       <c r="J6" t="n">
-        <v>0.005993888786258389</v>
+        <v>0.0060231279966876</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2052336041890688</v>
+        <v>-0.2051175338948052</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1017456340425877</v>
+        <v>-0.1010249767322107</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03617844233155791</v>
+        <v>0.03697575058174365</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07464152036126991</v>
+        <v>-0.07411438993979522</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.05355812649770588</v>
+        <v>-0.05350350709111668</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.09258901411685946</v>
+        <v>-0.09158713153185113</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01008551027646696</v>
+        <v>-0.009562587926011402</v>
       </c>
     </row>
     <row r="7">
@@ -792,52 +797,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.1355313016302211</v>
+        <v>-0.1355317025116319</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02817883678221163</v>
+        <v>0.02807453971139579</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.08553587651272015</v>
+        <v>-0.08512695739713484</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1766286529237518</v>
+        <v>-0.1770074714359857</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0922012884699336</v>
+        <v>-0.09632840393371352</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06282255976975112</v>
+        <v>-0.06254408391451827</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1703929093164277</v>
+        <v>-0.1696752031290689</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.07989313240489164</v>
+        <v>-0.079030023058152</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04395240665728846</v>
+        <v>0.04379800438665289</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01988565738696616</v>
+        <v>-0.01961027333717222</v>
       </c>
       <c r="M7" t="n">
-        <v>0.00341186441318024</v>
+        <v>0.0005319972727095799</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03897788652877074</v>
+        <v>-0.03764544846240821</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01561696923246418</v>
+        <v>0.01557371636045965</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.09441307494806858</v>
+        <v>-0.0930154219528144</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1626251034195711</v>
+        <v>-0.1633904206876969</v>
       </c>
     </row>
     <row r="8">
@@ -847,52 +852,52 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.1218085247248904</v>
+        <v>-0.1216160843892629</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1450430271331672</v>
+        <v>0.1447840044277443</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2703772862496451</v>
+        <v>-0.27028864358845</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06511969502461017</v>
+        <v>-0.06496619955148661</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0508629321073147</v>
+        <v>-0.05084429995402844</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.06282255976975112</v>
+        <v>-0.06254408391451827</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03437650187587582</v>
+        <v>0.03447429929511828</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.07429885744040775</v>
+        <v>-0.0742956318273451</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3125845145089784</v>
+        <v>-0.3126235114408756</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1041832625076397</v>
+        <v>0.1039162491246015</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05434876315504823</v>
+        <v>0.05433778738869455</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04447470910481596</v>
+        <v>0.04342852404811288</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.08039076614558678</v>
+        <v>-0.08039064147068299</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1004883464299043</v>
+        <v>-0.1006669429915227</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1915602126733785</v>
+        <v>-0.1915084906388044</v>
       </c>
     </row>
     <row r="9">
@@ -902,52 +907,52 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.08073821517666842</v>
+        <v>-0.08052004971915319</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.1340585348376442</v>
+        <v>-0.1341678821627228</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0805183112230478</v>
+        <v>-0.08049336060092532</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2706328631736525</v>
+        <v>0.2707204419789068</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1360656205524013</v>
+        <v>-0.1359932351809089</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1703929093164277</v>
+        <v>-0.1696752031290689</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03437650187587582</v>
+        <v>0.03447429929511828</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.04491763295939211</v>
+        <v>-0.04491847771452343</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2005544561451796</v>
+        <v>-0.2006872091723927</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2244847333167871</v>
+        <v>-0.2246387655889052</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03101882932359859</v>
+        <v>0.03107542727373782</v>
       </c>
       <c r="N9" t="n">
-        <v>0.189215330404692</v>
+        <v>0.1882032116529532</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1257232227425618</v>
+        <v>-0.1257564663197375</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.008512059613794015</v>
+        <v>-0.008764547601235594</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.07511561428941303</v>
+        <v>-0.07503580420373911</v>
       </c>
     </row>
     <row r="10">
@@ -957,52 +962,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.05804995049247332</v>
+        <v>0.05792992845644979</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.05074299149698708</v>
+        <v>-0.05046929824311092</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1115211311519058</v>
+        <v>0.1122835094873397</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03348565619808058</v>
+        <v>-0.03364491300047812</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005993888786258389</v>
+        <v>0.0060231279966876</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07989313240489164</v>
+        <v>-0.079030023058152</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.07429885744040775</v>
+        <v>-0.0742956318273451</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04491763295939211</v>
+        <v>-0.04491847771452343</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1325632685616241</v>
+        <v>-0.1322592061843188</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1558932506956993</v>
+        <v>0.1559190592617124</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1762600094056756</v>
+        <v>-0.1762765550126366</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1278703532491723</v>
+        <v>-0.1252386599281711</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03673196996612161</v>
+        <v>0.03797579824256751</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1194696439482417</v>
+        <v>-0.1197918189239087</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1726766013534738</v>
+        <v>-0.1726388510991327</v>
       </c>
     </row>
     <row r="11">
@@ -1012,52 +1017,52 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.048575392882437</v>
+        <v>0.04863709424635373</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.0325394223372264</v>
+        <v>-0.03270193011859826</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07518360906744938</v>
+        <v>-0.07515773676517375</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1000576880413598</v>
+        <v>0.100031692817402</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2052336041890688</v>
+        <v>-0.2051175338948052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.04395240665728846</v>
+        <v>0.04379800438665289</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3125845145089784</v>
+        <v>-0.3126235114408756</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2005544561451796</v>
+        <v>-0.2006872091723927</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1325632685616241</v>
+        <v>-0.1322592061843188</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.05861149464052461</v>
+        <v>-0.05879111260399703</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1888806556268003</v>
+        <v>-0.1889588258437239</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02278123468137408</v>
+        <v>-0.0239226357509733</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.03685720663704715</v>
+        <v>-0.03686070835404685</v>
       </c>
       <c r="P11" t="n">
-        <v>0.05879363850162724</v>
+        <v>0.05866833871363246</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.1124655774179182</v>
+        <v>0.1123733949015214</v>
       </c>
     </row>
     <row r="12">
@@ -1067,52 +1072,52 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-0.09626554706117064</v>
+        <v>-0.09646120289282363</v>
       </c>
       <c r="C12" t="n">
-        <v>0.08546242073465947</v>
+        <v>0.0850583532950671</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06023104328812207</v>
+        <v>0.0601751418402045</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2007454882679256</v>
+        <v>-0.2006260126681326</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1017456340425877</v>
+        <v>-0.1010249767322107</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.01988565738696616</v>
+        <v>-0.01961027333717222</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1041832625076397</v>
+        <v>0.1039162491246015</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2244847333167871</v>
+        <v>-0.2246387655889052</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1558932506956993</v>
+        <v>0.1559190592617124</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.05861149464052461</v>
+        <v>-0.05879111260399703</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3909224457029915</v>
+        <v>-0.3908145774470582</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.009367460107063788</v>
+        <v>-0.008572532180948</v>
       </c>
       <c r="O12" t="n">
-        <v>0.003527835110508621</v>
+        <v>0.003614333146551238</v>
       </c>
       <c r="P12" t="n">
-        <v>0.001542296766971666</v>
+        <v>0.001573422529801383</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1673848330442073</v>
+        <v>-0.1673115237619863</v>
       </c>
     </row>
     <row r="13">
@@ -1122,52 +1127,52 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-0.1487156556928946</v>
+        <v>-0.1484183594555742</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0002664334074884053</v>
+        <v>-0.0001613377742980673</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.1478146495693051</v>
+        <v>-0.1478381907239498</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.03316880020480939</v>
+        <v>-0.03274517515127993</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03617844233155791</v>
+        <v>0.03697575058174365</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00341186441318024</v>
+        <v>0.0005319972727095799</v>
       </c>
       <c r="H13" t="n">
-        <v>0.05434876315504823</v>
+        <v>0.05433778738869455</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03101882932359859</v>
+        <v>0.03107542727373782</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1762600094056756</v>
+        <v>-0.1762765550126366</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.1888806556268003</v>
+        <v>-0.1889588258437239</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3909224457029915</v>
+        <v>-0.3908145774470582</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1200611227331643</v>
+        <v>0.1192829306269266</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2608616456486035</v>
+        <v>-0.2608347518398468</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.09277448636282806</v>
+        <v>-0.09212065183383804</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02960404381435228</v>
+        <v>0.02997328526288242</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1182,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-0.151685918228377</v>
+        <v>-0.1526585001533138</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0003474839180459978</v>
+        <v>0.0004577684142593403</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1774285833250369</v>
+        <v>-0.1768872410707682</v>
       </c>
       <c r="E14" t="n">
-        <v>0.006469681501478089</v>
+        <v>0.005467479294178872</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.07464152036126991</v>
+        <v>-0.07411438993979522</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.03897788652877074</v>
+        <v>-0.03764544846240821</v>
       </c>
       <c r="H14" t="n">
-        <v>0.04447470910481596</v>
+        <v>0.04342852404811288</v>
       </c>
       <c r="I14" t="n">
-        <v>0.189215330404692</v>
+        <v>0.1882032116529532</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1278703532491723</v>
+        <v>-0.1252386599281711</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02278123468137408</v>
+        <v>-0.0239226357509733</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.009367460107063788</v>
+        <v>-0.008572532180948</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1200611227331643</v>
+        <v>0.1192829306269266</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2059419450098975</v>
+        <v>-0.2053986518795984</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.04682819099166641</v>
+        <v>-0.04748449021483139</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1335880969721098</v>
+        <v>-0.1345432514494057</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1237,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.100229179268183</v>
+        <v>0.1002349950463313</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.1868374340694986</v>
+        <v>-0.1867170118357693</v>
       </c>
       <c r="D15" t="n">
-        <v>0.01493214900673709</v>
+        <v>0.01536554336623541</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1812667506864618</v>
+        <v>-0.1812409067511802</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.05355812649770588</v>
+        <v>-0.05350350709111668</v>
       </c>
       <c r="G15" t="n">
-        <v>0.01561696923246418</v>
+        <v>0.01557371636045965</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08039076614558678</v>
+        <v>-0.08039064147068299</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1257232227425618</v>
+        <v>-0.1257564663197375</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03673196996612161</v>
+        <v>0.03797579824256751</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.03685720663704715</v>
+        <v>-0.03686070835404685</v>
       </c>
       <c r="L15" t="n">
-        <v>0.003527835110508621</v>
+        <v>0.003614333146551238</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2608616456486035</v>
+        <v>-0.2608347518398468</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2059419450098975</v>
+        <v>-0.2053986518795984</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0.06905705047985891</v>
+        <v>0.06874828026171384</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1275246050553445</v>
+        <v>0.1273779003338536</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1292,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.1113857471036297</v>
+        <v>-0.1117956020591704</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1993983041643551</v>
+        <v>-0.1994977896287584</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.01156395777272529</v>
+        <v>-0.01183214182746893</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1351991514369207</v>
+        <v>-0.135727445255063</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.09258901411685946</v>
+        <v>-0.09158713153185113</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.09441307494806858</v>
+        <v>-0.0930154219528144</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1004883464299043</v>
+        <v>-0.1006669429915227</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.008512059613794015</v>
+        <v>-0.008764547601235594</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1194696439482417</v>
+        <v>-0.1197918189239087</v>
       </c>
       <c r="K16" t="n">
-        <v>0.05879363850162724</v>
+        <v>0.05866833871363246</v>
       </c>
       <c r="L16" t="n">
-        <v>0.001542296766971666</v>
+        <v>0.001573422529801383</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.09277448636282806</v>
+        <v>-0.09212065183383804</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04682819099166641</v>
+        <v>-0.04748449021483139</v>
       </c>
       <c r="O16" t="n">
-        <v>0.06905705047985891</v>
+        <v>0.06874828026171384</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1372291405893051</v>
+        <v>-0.1375950664560569</v>
       </c>
     </row>
     <row r="17">
@@ -1342,49 +1347,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.05272643549990629</v>
+        <v>0.05294858795777122</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.2514850807914431</v>
+        <v>-0.2514247683491527</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1414652077917651</v>
+        <v>-0.1414849592482887</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.06401031662561422</v>
+        <v>-0.06361767074921351</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.01008551027646696</v>
+        <v>-0.009562587926011402</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1626251034195711</v>
+        <v>-0.1633904206876969</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1915602126733785</v>
+        <v>-0.1915084906388044</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.07511561428941303</v>
+        <v>-0.07503580420373911</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1726766013534738</v>
+        <v>-0.1726388510991327</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1124655774179182</v>
+        <v>0.1123733949015214</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1673848330442073</v>
+        <v>-0.1673115237619863</v>
       </c>
       <c r="M17" t="n">
-        <v>0.02960404381435228</v>
+        <v>0.02997328526288242</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1335880969721098</v>
+        <v>-0.1345432514494057</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1275246050553445</v>
+        <v>0.1273779003338536</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1372291405893051</v>
+        <v>-0.1375950664560569</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
